--- a/results/样本量变化表.xlsx
+++ b/results/样本量变化表.xlsx
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="C54" s="14" t="n">
-        <v>0.787</v>
+        <v>0.785</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="C55" s="14" t="n">
-        <v>0.787</v>
+        <v>0.785</v>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>

--- a/results/样本量变化表.xlsx
+++ b/results/样本量变化表.xlsx
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="C54" s="14" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="C55" s="14" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>

--- a/results/样本量变化表.xlsx
+++ b/results/样本量变化表.xlsx
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>4.57</v>
+        <v>4.56</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>4.57</v>
+        <v>4.56</v>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="C54" s="14" t="n">
-        <v>0.785</v>
+        <v>0.783</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="C55" s="14" t="n">
-        <v>0.785</v>
+        <v>0.783</v>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>

--- a/results/样本量变化表.xlsx
+++ b/results/样本量变化表.xlsx
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>4.56</v>
+        <v>4.62</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>4.56</v>
+        <v>4.62</v>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="C54" s="14" t="n">
-        <v>0.783</v>
+        <v>0.793</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="C55" s="14" t="n">
-        <v>0.783</v>
+        <v>0.793</v>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>

--- a/results/样本量变化表.xlsx
+++ b/results/样本量变化表.xlsx
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>4.62</v>
+        <v>4.59</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>4.62</v>
+        <v>4.59</v>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="C54" s="14" t="n">
-        <v>0.793</v>
+        <v>0.789</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="C55" s="14" t="n">
-        <v>0.793</v>
+        <v>0.789</v>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>

--- a/results/样本量变化表.xlsx
+++ b/results/样本量变化表.xlsx
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>4.59</v>
+        <v>4.57</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>4.59</v>
+        <v>4.57</v>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="C54" s="14" t="n">
-        <v>0.789</v>
+        <v>0.785</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="C55" s="14" t="n">
-        <v>0.789</v>
+        <v>0.785</v>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>

--- a/results/样本量变化表.xlsx
+++ b/results/样本量变化表.xlsx
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="C54" s="14" t="n">
-        <v>0.785</v>
+        <v>0.914</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="C55" s="14" t="n">
-        <v>0.785</v>
+        <v>0.914</v>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>

--- a/results/样本量变化表.xlsx
+++ b/results/样本量变化表.xlsx
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D27" s="5" t="n"/>
     </row>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="C49" s="11" t="n">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="C52" s="11" t="n">
-        <v>4.57</v>
+        <v>4.3</v>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="C53" s="11" t="n">
-        <v>4.57</v>
+        <v>4.3</v>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="C54" s="14" t="n">
-        <v>0.914</v>
+        <v>0.86</v>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="C55" s="14" t="n">
-        <v>0.914</v>
+        <v>0.86</v>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>

--- a/results/样本量变化表.xlsx
+++ b/results/样本量变化表.xlsx
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>

--- a/results/样本量变化表.xlsx
+++ b/results/样本量变化表.xlsx
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
